--- a/seat-extension/seat-final-template.xlsx
+++ b/seat-extension/seat-final-template.xlsx
@@ -269,7 +269,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -322,15 +322,18 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -340,10 +343,15 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -874,11 +882,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:F47"/>
+  <dimension ref="B2:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" style="6" min="1" max="1"/>
-    <col width="18" customWidth="1" style="6" min="2" max="2"/>
+    <col width="22" customWidth="1" style="6" min="2" max="2"/>
     <col width="46" customWidth="1" style="6" min="3" max="3"/>
     <col width="40" customWidth="1" style="6" min="4" max="4"/>
     <col width="44" customWidth="1" style="6" min="5" max="5"/>
@@ -888,14 +896,14 @@
     <row r="2" ht="34" customHeight="1" s="6">
       <c r="B2" s="14" t="inlineStr">
         <is>
-          <t>판단 기준 · 수집 기준 · 정렬 기준</t>
+          <t>판단 기준 · 수집 기준</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" s="6">
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>LX3 / ME1 / MX5 2·3열 전동 시트 작동 위험 상황 관련 게시물 — 이 파일의 글을 어떤 기준으로 모으고, 고르고, 관련도를 매기고, 정렬했는지 정리한 시트입니다.</t>
+          <t>LX3 / ME1 / MX5 2·3열 전동 시트 작동 위험 상황 관련 게시물 — 이 파일의 글을 어떤 기준으로 모으고, 고르고, 관련도를 매겼는지 정리한 시트입니다.</t>
         </is>
       </c>
     </row>
@@ -934,10 +942,8 @@
       </c>
     </row>
     <row r="7" ht="78" customHeight="1" s="6">
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
+      <c r="B7" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
@@ -962,7 +968,7 @@
       </c>
     </row>
     <row r="8" ht="78" customHeight="1" s="6">
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>85~95%</t>
         </is>
@@ -991,7 +997,7 @@
       </c>
     </row>
     <row r="9" ht="78" customHeight="1" s="6">
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>70~84%</t>
         </is>
@@ -1020,7 +1026,7 @@
       </c>
     </row>
     <row r="10" ht="78" customHeight="1" s="6">
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>40~69%</t>
         </is>
@@ -1042,14 +1048,14 @@
 "전동시트 끼임 사고 기사 공유합니다"</t>
         </is>
       </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>파랑</t>
         </is>
       </c>
     </row>
     <row r="11" ht="78" customHeight="1" s="6">
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>10~39%</t>
         </is>
@@ -1070,14 +1076,14 @@
 "3열 전동 폴딩이 가끔 안 된다"</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>파랑</t>
         </is>
       </c>
     </row>
     <row r="12" ht="78" customHeight="1" s="6">
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>0~9%</t>
         </is>
@@ -1098,19 +1104,18 @@
 "2열 카시트 추천 부탁드려요"</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>파랑</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="72" customHeight="1" s="6">
-      <c r="B13" s="23" t="inlineStr">
+    <row r="13" ht="56" customHeight="1" s="6">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>· 70% 이상은 빨강, 70% 미만은 파랑으로 표시합니다(엑셀 조건부 서식 · 값을 고치면 색도 바뀜).
 · 같은 구간 안에서는 장면·결과가 구체적일수록, 아이·반려동물 등 피해 대상이 분명할수록, 같은 일이 반복될수록 위쪽 점수를 줍니다.
-· 관련도는 본문 판독 내용(제목·주요내용 요약·상황 분류·본문 앞부분)을 보고 매깁니다. 판독된 내용에 없는 사실은 근거로 쓰지 않습니다.
-· '꼭 넣을 글'(담당자가 지정한 글)은 관련도와 상관없이 최종 확정에 포함합니다.</t>
+· 관련도는 본문 판독 내용(제목·주요내용 요약·상황 분류·본문 앞부분)을 보고 매깁니다. 판독된 내용에 없는 사실은 근거로 쓰지 않습니다.</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1150,7 @@
       <c r="F16" s="17" t="inlineStr"/>
     </row>
     <row r="17" ht="52" customHeight="1" s="6">
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>① 전동 시트 작동 이슈</t>
         </is>
@@ -1165,10 +1170,10 @@
           <t>전동 트렁크(테일게이트)·도어·선루프·창문 등 다른 장치 이슈, 카시트·가죽·열선 등 작동과 무관한 시트 이야기</t>
         </is>
       </c>
-      <c r="F17" s="25" t="inlineStr"/>
+      <c r="F17" s="26" t="inlineStr"/>
     </row>
     <row r="18" ht="52" customHeight="1" s="6">
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>② 작동 중 사고 발생</t>
         </is>
@@ -1188,10 +1193,10 @@
           <t>사고 없이 가정·우려만 있음</t>
         </is>
       </c>
-      <c r="F18" s="25" t="inlineStr"/>
+      <c r="F18" s="26" t="inlineStr"/>
     </row>
     <row r="19" ht="52" customHeight="1" s="6">
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>③ 위험성·안전사고 우려</t>
         </is>
@@ -1211,10 +1216,10 @@
           <t>불편·고장만 말함</t>
         </is>
       </c>
-      <c r="F19" s="25" t="inlineStr"/>
+      <c r="F19" s="26" t="inlineStr"/>
     </row>
     <row r="20" ht="52" customHeight="1" s="6">
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>④ 타 이슈 중 일부 언급</t>
         </is>
@@ -1234,12 +1239,12 @@
           <t>위험·사고·우려 문장이 전혀 없음</t>
         </is>
       </c>
-      <c r="F20" s="25" t="inlineStr"/>
+      <c r="F20" s="26" t="inlineStr"/>
     </row>
     <row r="21" ht="40" customHeight="1" s="6">
-      <c r="B21" s="23" t="inlineStr">
-        <is>
-          <t>· 최종 확정 = ① 에 해당하고, ②·③·④ 중 하나 이상에 해당하는 글. 담당자가 지정한 '꼭 넣을 글'은 항상 포함합니다.
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>· 최종 확정 = ① 에 해당하고, ②·③·④ 중 하나 이상에 해당하는 글.
 · 최종 확정 여부는 4항목 판정으로 정하며, 관련도는 함께 참고용으로 표시합니다.</t>
         </is>
       </c>
@@ -1262,12 +1267,12 @@
           <t>기준</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr"/>
-      <c r="E24" s="17" t="inlineStr"/>
-      <c r="F24" s="17" t="inlineStr"/>
+      <c r="D24" s="27" t="n"/>
+      <c r="E24" s="27" t="n"/>
+      <c r="F24" s="28" t="n"/>
     </row>
     <row r="25" ht="50" customHeight="1" s="6">
-      <c r="B25" s="24" t="inlineStr">
+      <c r="B25" s="29" t="inlineStr">
         <is>
           <t>수집 기간</t>
         </is>
@@ -1277,12 +1282,12 @@
           <t>{{period}}</t>
         </is>
       </c>
-      <c r="D25" s="26" t="n"/>
-      <c r="E25" s="26" t="n"/>
-      <c r="F25" s="26" t="n"/>
+      <c r="D25" s="30" t="n"/>
+      <c r="E25" s="30" t="n"/>
+      <c r="F25" s="30" t="n"/>
     </row>
     <row r="26" ht="180" customHeight="1" s="6">
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B26" s="29" t="inlineStr">
         <is>
           <t>조사 채널</t>
         </is>
@@ -1292,307 +1297,110 @@
           <t>{{cafes}}</t>
         </is>
       </c>
-      <c r="D26" s="26" t="n"/>
-      <c r="E26" s="26" t="n"/>
-      <c r="F26" s="26" t="n"/>
-    </row>
-    <row r="27" ht="60" customHeight="1" s="6">
-      <c r="B27" s="24" t="inlineStr">
-        <is>
-          <t>검색어</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="inlineStr">
-        <is>
-          <t>{{queries}}</t>
-        </is>
-      </c>
-      <c r="D27" s="26" t="n"/>
-      <c r="E27" s="26" t="n"/>
-      <c r="F27" s="26" t="n"/>
-    </row>
-    <row r="28" ht="110" customHeight="1" s="6">
-      <c r="B28" s="24" t="inlineStr">
-        <is>
-          <t>1차 자동 선별</t>
-        </is>
-      </c>
-      <c r="C28" s="19" t="inlineStr">
-        <is>
-          <t>{{words}}</t>
-        </is>
-      </c>
-      <c r="D28" s="26" t="n"/>
-      <c r="E28" s="26" t="n"/>
-      <c r="F28" s="26" t="n"/>
-    </row>
-    <row r="29" ht="44" customHeight="1" s="6">
-      <c r="B29" s="24" t="inlineStr">
-        <is>
-          <t>내용 재검토</t>
-        </is>
-      </c>
-      <c r="C29" s="19" t="inlineStr">
-        <is>
-          <t>체크되지 않은 글도 제목·미리보기(검색 목록의 본문 일부)를 단어가 아닌 내용으로 다시 검토하고, 시트·안전 단서가 있으면 본문까지 읽도록 체크(애매하면 체크).</t>
-        </is>
-      </c>
-      <c r="D29" s="26" t="n"/>
-      <c r="E29" s="26" t="n"/>
-      <c r="F29" s="26" t="n"/>
-    </row>
-    <row r="30" ht="44" customHeight="1" s="6">
-      <c r="B30" s="24" t="inlineStr">
-        <is>
-          <t>본문 판독</t>
+      <c r="D26" s="30" t="n"/>
+      <c r="E26" s="30" t="n"/>
+      <c r="F26" s="30" t="n"/>
+    </row>
+    <row r="28" ht="24" customHeight="1" s="6">
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>4. 포함 여부(온라인동향 / 로데이터) · 누락 사유 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1" s="6">
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>기준</t>
+        </is>
+      </c>
+      <c r="D29" s="27" t="n"/>
+      <c r="E29" s="27" t="n"/>
+      <c r="F29" s="28" t="n"/>
+    </row>
+    <row r="30" ht="34" customHeight="1" s="6">
+      <c r="B30" s="29" t="inlineStr">
+        <is>
+          <t>표기</t>
         </is>
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>체크한 글은 게시글을 열어 본문을 읽고, 본문 내용으로 관련 여부·상황 분류(실제 사고/아차 사고/위험 우려/문의/기사·공지 공유)·주요내용 요약·누락 사유를 작성.</t>
-        </is>
-      </c>
-      <c r="D30" s="26" t="n"/>
-      <c r="E30" s="26" t="n"/>
-      <c r="F30" s="26" t="n"/>
-    </row>
-    <row r="31" ht="40" customHeight="1" s="6">
-      <c r="B31" s="24" t="inlineStr">
-        <is>
-          <t>꼭 넣을 글</t>
+          <t>온라인동향 / 로데이터 순서로 Y(파랑) · N(빨강). 로데이터에 없는 글로는 일일동향을 쓸 수 없어 'Y / N' 조합은 나오지 않음.</t>
+        </is>
+      </c>
+      <c r="D30" s="30" t="n"/>
+      <c r="E30" s="30" t="n"/>
+      <c r="F30" s="30" t="n"/>
+    </row>
+    <row r="31" ht="44" customHeight="1" s="6">
+      <c r="B31" s="29" t="inlineStr">
+        <is>
+          <t>누락 사유</t>
         </is>
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t>{{must}}</t>
-        </is>
-      </c>
-      <c r="D31" s="26" t="n"/>
-      <c r="E31" s="26" t="n"/>
-      <c r="F31" s="26" t="n"/>
-    </row>
-    <row r="33" ht="24" customHeight="1" s="6">
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>4. 포함 여부(온라인동향 / 로데이터) · 누락 사유 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1" s="6">
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>기준</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr"/>
-      <c r="E34" s="17" t="inlineStr"/>
-      <c r="F34" s="17" t="inlineStr"/>
-    </row>
-    <row r="35" ht="120" customHeight="1" s="6">
-      <c r="B35" s="24" t="inlineStr">
-        <is>
-          <t>비교 파일</t>
-        </is>
-      </c>
-      <c r="C35" s="19" t="inlineStr">
-        <is>
-          <t>{{compareFiles}}</t>
-        </is>
-      </c>
-      <c r="D35" s="26" t="n"/>
-      <c r="E35" s="26" t="n"/>
-      <c r="F35" s="26" t="n"/>
-    </row>
-    <row r="36" ht="44" customHeight="1" s="6">
-      <c r="B36" s="24" t="inlineStr">
-        <is>
-          <t>같은 글 판단</t>
-        </is>
-      </c>
-      <c r="C36" s="19" t="inlineStr">
-        <is>
-          <t>카페 영문 주소 + 글번호로 비교 (주소 뒤 ?art=… 같은 꼬리, f-e/cafes/번호/articles/번호 새 주소 모양이 달라도 같은 글). naver.me 짧은 주소는 실제 카페 주소로 풀어서 비교.</t>
-        </is>
-      </c>
-      <c r="D36" s="26" t="n"/>
-      <c r="E36" s="26" t="n"/>
-      <c r="F36" s="26" t="n"/>
-    </row>
-    <row r="37" ht="34" customHeight="1" s="6">
-      <c r="B37" s="24" t="inlineStr">
-        <is>
-          <t>표기</t>
-        </is>
-      </c>
-      <c r="C37" s="19" t="inlineStr">
-        <is>
-          <t>온라인동향 / 로데이터 순서로 Y(파랑) · N(빨강). 로데이터에 없는 글로는 일일동향을 쓸 수 없어 'Y / N' 조합은 나오지 않음.</t>
-        </is>
-      </c>
-      <c r="D37" s="26" t="n"/>
-      <c r="E37" s="26" t="n"/>
-      <c r="F37" s="26" t="n"/>
-    </row>
-    <row r="38" ht="44" customHeight="1" s="6">
-      <c r="B38" s="24" t="inlineStr">
-        <is>
-          <t>누락 사유</t>
-        </is>
-      </c>
-      <c r="C38" s="19" t="inlineStr">
-        <is>
           <t>온라인 동향에 없는(N) 글만 작성. 글 내용에 근거해 '~로 추정' 으로 끝맺음(실제 사고가 아닌 우려 수준, 아차 상황, 단순 문의, 기사 공유, 로데이터엔 있으나 보고 기준 미달 등).</t>
         </is>
       </c>
-      <c r="D38" s="26" t="n"/>
-      <c r="E38" s="26" t="n"/>
-      <c r="F38" s="26" t="n"/>
-    </row>
-    <row r="39" ht="44" customHeight="1" s="6">
-      <c r="B39" s="24" t="inlineStr">
+      <c r="D31" s="30" t="n"/>
+      <c r="E31" s="30" t="n"/>
+      <c r="F31" s="30" t="n"/>
+    </row>
+    <row r="32" ht="44" customHeight="1" s="6">
+      <c r="B32" s="29" t="inlineStr">
         <is>
           <t>동호회 모니터링 시작일</t>
         </is>
       </c>
-      <c r="C39" s="19" t="inlineStr">
+      <c r="C32" s="19" t="inlineStr">
         <is>
           <t>{{monitorStart}}</t>
         </is>
       </c>
-      <c r="D39" s="26" t="n"/>
-      <c r="E39" s="26" t="n"/>
-      <c r="F39" s="26" t="n"/>
-    </row>
-    <row r="40" ht="44" customHeight="1" s="6">
-      <c r="B40" s="24" t="inlineStr">
+      <c r="D32" s="30" t="n"/>
+      <c r="E32" s="30" t="n"/>
+      <c r="F32" s="30" t="n"/>
+    </row>
+    <row r="33" ht="44" customHeight="1" s="6">
+      <c r="B33" s="29" t="inlineStr">
         <is>
           <t>로데이터 작성 시작일</t>
         </is>
       </c>
-      <c r="C40" s="19" t="inlineStr">
+      <c r="C33" s="19" t="inlineStr">
         <is>
           <t>{{rawStart}}</t>
         </is>
       </c>
-      <c r="D40" s="26" t="n"/>
-      <c r="E40" s="26" t="n"/>
-      <c r="F40" s="26" t="n"/>
-    </row>
-    <row r="42" ht="24" customHeight="1" s="6">
-      <c r="B42" s="16" t="inlineStr">
-        <is>
-          <t>5. 정렬(소팅) 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1" s="6">
-      <c r="B43" s="17" t="inlineStr">
-        <is>
-          <t>순서</t>
-        </is>
-      </c>
-      <c r="C43" s="17" t="inlineStr">
-        <is>
-          <t>기준</t>
-        </is>
-      </c>
-      <c r="D43" s="17" t="inlineStr"/>
-      <c r="E43" s="17" t="inlineStr"/>
-      <c r="F43" s="17" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="B44" s="24" t="inlineStr">
-        <is>
-          <t>1순위</t>
-        </is>
-      </c>
-      <c r="C44" s="19" t="inlineStr">
-        <is>
-          <t>차종 순: LX3(팰리세이드) → ME1(아이오닉9) → MX5(싼타페)</t>
-        </is>
-      </c>
-      <c r="D44" s="26" t="n"/>
-      <c r="E44" s="26" t="n"/>
-      <c r="F44" s="26" t="n"/>
-    </row>
-    <row r="45">
-      <c r="B45" s="24" t="inlineStr">
-        <is>
-          <t>2순위</t>
-        </is>
-      </c>
-      <c r="C45" s="19" t="inlineStr">
-        <is>
-          <t>같은 차종 안에서 게시일이 오래된 글부터</t>
-        </is>
-      </c>
-      <c r="D45" s="26" t="n"/>
-      <c r="E45" s="26" t="n"/>
-      <c r="F45" s="26" t="n"/>
-    </row>
-    <row r="46">
-      <c r="B46" s="24" t="inlineStr">
-        <is>
-          <t>3순위</t>
-        </is>
-      </c>
-      <c r="C46" s="19" t="inlineStr">
-        <is>
-          <t>같은 날 글은 동호회 목록 순서대로</t>
-        </is>
-      </c>
-      <c r="D46" s="26" t="n"/>
-      <c r="E46" s="26" t="n"/>
-      <c r="F46" s="26" t="n"/>
-    </row>
-    <row r="47">
-      <c r="B47" s="24" t="inlineStr">
-        <is>
-          <t>순번</t>
-        </is>
-      </c>
-      <c r="C47" s="19" t="inlineStr">
-        <is>
-          <t>정렬한 순서대로 1번부터 매김 (B열)</t>
-        </is>
-      </c>
-      <c r="D47" s="26" t="n"/>
-      <c r="E47" s="26" t="n"/>
-      <c r="F47" s="26" t="n"/>
+      <c r="D33" s="30" t="n"/>
+      <c r="E33" s="30" t="n"/>
+      <c r="F33" s="30" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="C39:F39"/>
+  <mergeCells count="16">
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="B28:F28"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="C29:F29"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="B23:F23"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C24:F24"/>
     <mergeCell ref="B13:F13"/>
-    <mergeCell ref="C45:F45"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C47:F47"/>
-    <mergeCell ref="C44:F44"/>
-    <mergeCell ref="C40:F40"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="C46:F46"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C36:F36"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seat-extension/seat-final-template.xlsx
+++ b/seat-extension/seat-final-template.xlsx
@@ -882,7 +882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:F33"/>
+  <dimension ref="B2:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" style="6" min="1" max="1"/>
@@ -1338,30 +1338,30 @@
       <c r="E30" s="30" t="n"/>
       <c r="F30" s="30" t="n"/>
     </row>
-    <row r="31" ht="44" customHeight="1" s="6">
+    <row r="31" ht="64" customHeight="1" s="6">
       <c r="B31" s="29" t="inlineStr">
         <is>
-          <t>누락 사유</t>
+          <t>누락 사유 (N / N)</t>
         </is>
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t>온라인 동향에 없는(N) 글만 작성. 글 내용에 근거해 '~로 추정' 으로 끝맺음(실제 사고가 아닌 우려 수준, 아차 상황, 단순 문의, 기사 공유, 로데이터엔 있으나 보고 기준 미달 등).</t>
+          <t>로데이터는 실제로 발생한 사고·품질 이슈만 수집해 왔고, 일어나지 않은 일(위험 우려·가능성, 주의 당부, 끼일 뻔한 아차 상황, 작동 방식 문의, 기사·공지 공유 등)은 수집하지 않았음. 로데이터에도 없는 글은 이 기준에 근거해 글 내용상 무엇이 실제로 일어나지 않은 일이었는지를 밝혀 '~로 추정' 으로 씀. 실제 사고가 있었던 글은 품질 이슈로 보지 않았을 이유(경미함·사용 부주의 등)를 씀.</t>
         </is>
       </c>
       <c r="D31" s="30" t="n"/>
       <c r="E31" s="30" t="n"/>
       <c r="F31" s="30" t="n"/>
     </row>
-    <row r="32" ht="44" customHeight="1" s="6">
+    <row r="32" ht="34" customHeight="1" s="6">
       <c r="B32" s="29" t="inlineStr">
         <is>
-          <t>동호회 모니터링 시작일</t>
+          <t>누락 사유 (N / Y)</t>
         </is>
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>{{monitorStart}}</t>
+          <t>로데이터에는 있으나 온라인 동향에 없는 글은 '로데이터에는 수집되었으나, …' 로 시작해 온라인 동향 보고에서 빠진 이유를 '~로 추정' 으로 씀.</t>
         </is>
       </c>
       <c r="D32" s="30" t="n"/>
@@ -1371,20 +1371,35 @@
     <row r="33" ht="44" customHeight="1" s="6">
       <c r="B33" s="29" t="inlineStr">
         <is>
-          <t>로데이터 작성 시작일</t>
+          <t>동호회 모니터링 시작일</t>
         </is>
       </c>
       <c r="C33" s="19" t="inlineStr">
         <is>
-          <t>{{rawStart}}</t>
+          <t>{{monitorStart}}</t>
         </is>
       </c>
       <c r="D33" s="30" t="n"/>
       <c r="E33" s="30" t="n"/>
       <c r="F33" s="30" t="n"/>
     </row>
+    <row r="34" ht="44" customHeight="1" s="6">
+      <c r="B34" s="29" t="inlineStr">
+        <is>
+          <t>로데이터 작성 시작일</t>
+        </is>
+      </c>
+      <c r="C34" s="19" t="inlineStr">
+        <is>
+          <t>{{rawStart}}</t>
+        </is>
+      </c>
+      <c r="D34" s="30" t="n"/>
+      <c r="E34" s="30" t="n"/>
+      <c r="F34" s="30" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="B2:F2"/>
@@ -1395,6 +1410,7 @@
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C34:F34"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="C25:F25"/>

--- a/seat-extension/seat-final-template.xlsx
+++ b/seat-extension/seat-final-template.xlsx
@@ -238,7 +238,9 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin">
+        <color rgb="FFD9DDE3"/>
+      </right>
       <top style="thin">
         <color rgb="FFD9DDE3"/>
       </top>
@@ -249,9 +251,7 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color rgb="FFD9DDE3"/>
-      </right>
+      <right/>
       <top style="thin">
         <color rgb="FFD9DDE3"/>
       </top>
@@ -269,7 +269,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -310,6 +310,21 @@
     <xf numFmtId="9" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
@@ -343,18 +358,15 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -770,84 +782,86 @@
   <dimension ref="B3:K4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col width="5.5" bestFit="1" customWidth="1" style="6" min="2" max="2"/>
-    <col width="31.83203125" customWidth="1" style="6" min="4" max="4"/>
-    <col width="17.6640625" bestFit="1" customWidth="1" style="6" min="5" max="5"/>
-    <col width="40" bestFit="1" customWidth="1" style="6" min="6" max="7"/>
-    <col width="38" customWidth="1" style="6" min="7" max="7"/>
-    <col width="60" customWidth="1" style="6" min="8" max="8"/>
-    <col width="22" bestFit="1" customWidth="1" style="6" min="9" max="9"/>
-    <col width="60" bestFit="1" customWidth="1" style="6" min="10" max="10"/>
-    <col width="12" customWidth="1" style="6" min="11" max="11"/>
+    <col width="2" customWidth="1" style="6" min="1" max="1"/>
+    <col width="6" bestFit="1" customWidth="1" style="6" min="2" max="2"/>
+    <col width="7" customWidth="1" style="6" min="3" max="3"/>
+    <col width="22" customWidth="1" style="6" min="4" max="4"/>
+    <col width="12" bestFit="1" customWidth="1" style="6" min="5" max="5"/>
+    <col width="56" bestFit="1" customWidth="1" style="6" min="6" max="7"/>
+    <col width="46" customWidth="1" style="6" min="7" max="7"/>
+    <col width="68" customWidth="1" style="6" min="8" max="8"/>
+    <col width="14" bestFit="1" customWidth="1" style="6" min="9" max="9"/>
+    <col width="80" bestFit="1" customWidth="1" style="6" min="10" max="10"/>
+    <col width="11" customWidth="1" style="6" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="3">
-      <c r="B3" s="7" t="inlineStr">
+    <row r="3" ht="36" customHeight="1" s="6">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>순번</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>차종</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>동호회명</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>게시일</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t>제목</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="14" t="inlineStr">
         <is>
           <t>주요내용 요약</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="14" t="inlineStr">
         <is>
           <t>온라인동향/로데이터 포함 여부</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t>미포함시 누락 사유</t>
         </is>
       </c>
-      <c r="K3" s="7" t="inlineStr">
+      <c r="K3" s="14" t="inlineStr">
         <is>
           <t>주제 관련도</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="8" t="n"/>
-      <c r="C4" s="8" t="n"/>
-      <c r="D4" s="9" t="n"/>
-      <c r="E4" s="10" t="n"/>
+    <row r="4" ht="66" customHeight="1" s="6">
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="16" t="n"/>
       <c r="F4" s="11" t="n"/>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>https://cafe.naver.com/</t>
         </is>
       </c>
       <c r="H4" s="11" t="n"/>
-      <c r="I4" s="8" t="n"/>
+      <c r="I4" s="15" t="n"/>
       <c r="J4" s="11" t="n"/>
-      <c r="K4" s="13" t="n"/>
+      <c r="K4" s="18" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="B3:K4"/>
@@ -886,7 +900,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" style="6" min="1" max="1"/>
-    <col width="22" customWidth="1" style="6" min="2" max="2"/>
+    <col width="30" customWidth="1" style="6" min="2" max="2"/>
     <col width="46" customWidth="1" style="6" min="3" max="3"/>
     <col width="40" customWidth="1" style="6" min="4" max="4"/>
     <col width="44" customWidth="1" style="6" min="5" max="5"/>
@@ -894,224 +908,224 @@
   </cols>
   <sheetData>
     <row r="2" ht="34" customHeight="1" s="6">
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>판단 기준 · 수집 기준</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" s="6">
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>LX3 / ME1 / MX5 2·3열 전동 시트 작동 위험 상황 관련 게시물 — 이 파일의 글을 어떤 기준으로 모으고, 고르고, 관련도를 매겼는지 정리한 시트입니다.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" s="6">
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>1. 주제 관련도(%) 판단 기준</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" s="6">
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>관련도</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>판단 기준</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>이 구간으로 보는 단서</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="22" t="inlineStr">
         <is>
           <t>표시</t>
         </is>
       </c>
     </row>
     <row r="7" ht="78" customHeight="1" s="6">
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>2·3열 전동 시트 작동 중 사람·반려동물·물건이 실제로 끼이거나 다친 사고가 명확함 (조사 주제와 완전 일치)</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="24" t="inlineStr">
         <is>
           <t>끼였다·눌렸다·다쳤다·멍·피·병원·파손 등 실제 결과가 있고, 그 원인이 2·3열 전동 시트 작동으로 명시됨</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="24" t="inlineStr">
         <is>
           <t>"3열에서 내리는데 2열 원터치 복귀에 아이 발이 끼여 멍이 들었다"
 "2열 폴딩에 강아지 다리가 눌려 병원에 다녀왔다"</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="25" t="inlineStr">
         <is>
           <t>빨강</t>
         </is>
       </c>
     </row>
     <row r="8" ht="78" customHeight="1" s="6">
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>85~95%</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>실제로 끼일 뻔·다칠 뻔한 아차 사고, 또는 구체적인 위험 상황 묘사</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>끼일 뻔·다칠 뻔·급히 멈춤·큰일 날 뻔 등 실제로 겪은 장면이 있음
 95%: 사고 직전·반복 경험 / 85%: 한 번의 짧은 아차 경험</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="24" t="inlineStr">
         <is>
           <t>"2열 폴딩 중 아이 손이 들어가 급히 멈췄다"
 "3열 복귀 버튼 눌렀는데 아이 발이 있어서 식겁했다"</t>
         </is>
       </c>
-      <c r="F8" s="20" t="inlineStr">
+      <c r="F8" s="25" t="inlineStr">
         <is>
           <t>빨강</t>
         </is>
       </c>
     </row>
     <row r="9" ht="78" customHeight="1" s="6">
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>70~84%</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>전동 시트 작동의 위험성·안전사고 우려·주의 당부, 안전장치(끼임 방지·센서·멈춤) 의문이 글의 주된 내용</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="24" t="inlineStr">
         <is>
           <t>위험하다·조심·불안·센서 없음·안 멈춤 등 우려가 글의 중심
 84%: 구체적인 상황을 들어 우려 / 70%: 짧은 우려·당부</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t>"센서가 없어 보이는데 아이 있는 집은 조심해야 할 것 같다"
 "원터치 복귀가 사람 있어도 안 멈추는 것 같아 불안하다"</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="25" t="inlineStr">
         <is>
           <t>빨강</t>
         </is>
       </c>
     </row>
     <row r="10" ht="78" customHeight="1" s="6">
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>40~69%</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>다른 이슈 사이에 위험이 일부 언급된 수준, 일반론, 관련 기사·리콜 공지 단순 공유</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>옵션·품질·출고 등 다른 주제 글 속 한두 문장, 기사 링크 공유
 69%: 위험 문장이 분명함 / 40%: 스치듯 언급</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E10" s="24" t="inlineStr">
         <is>
           <t>"옵션 후기… (중략) 3열 탈 때 발 조심하세요" 한 줄
 "전동시트 끼임 사고 기사 공유합니다"</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr">
+      <c r="F10" s="28" t="inlineStr">
         <is>
           <t>파랑</t>
         </is>
       </c>
     </row>
     <row r="11" ht="78" customHeight="1" s="6">
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>10~39%</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>전동 시트 작동 이야기지만 안전과 거의 무관 (기능 고장·편의성·소음 등)</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>느림·소음·작동 안 됨·버튼 위치 등 불편만 있고 사람·물건의 위험 언급이 없음</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t>"2열 폴딩 속도가 느리고 소리가 난다"
 "3열 전동 폴딩이 가끔 안 된다"</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="F11" s="28" t="inlineStr">
         <is>
           <t>파랑</t>
         </is>
       </c>
     </row>
     <row r="12" ht="78" customHeight="1" s="6">
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>0~9%</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>주제와 무관</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D12" s="24" t="inlineStr">
         <is>
           <t>전동 트렁크·도어·선루프·창문 등 다른 장치 이슈, 카시트·가죽·열선·통풍 등 작동과 무관한 시트 이야기</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="E12" s="24" t="inlineStr">
         <is>
           <t>"전동 트렁크 닫히다 손이 끼였다"
 "2열 카시트 추천 부탁드려요"</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F12" s="28" t="inlineStr">
         <is>
           <t>파랑</t>
         </is>
       </c>
     </row>
     <row r="13" ht="56" customHeight="1" s="6">
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>· 70% 이상은 빨강, 70% 미만은 파랑으로 표시합니다(엑셀 조건부 서식 · 값을 고치면 색도 바뀜).
 · 같은 구간 안에서는 장면·결과가 구체적일수록, 아이·반려동물 등 피해 대상이 분명할수록, 같은 일이 반복될수록 위쪽 점수를 줍니다.
@@ -1120,129 +1134,129 @@
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" s="6">
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>2. 최종 검수 4항목 · 최종 확정 조건</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" s="6">
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>검수 내용</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>포함으로 보는 경우</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>제외로 보는 경우</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr"/>
+      <c r="F16" s="30" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1" s="6">
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>① 전동 시트 작동 이슈</t>
         </is>
       </c>
-      <c r="C17" s="19" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>전동 시트 작동·조작(전동 폴딩·원터치 워크인·슬라이딩·리클라이닝·복귀)과 관련된 글인지</t>
         </is>
       </c>
-      <c r="D17" s="19" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>2·3열 전동 시트의 작동·조작이 글에 나옴</t>
         </is>
       </c>
-      <c r="E17" s="19" t="inlineStr">
+      <c r="E17" s="24" t="inlineStr">
         <is>
           <t>전동 트렁크(테일게이트)·도어·선루프·창문 등 다른 장치 이슈, 카시트·가죽·열선 등 작동과 무관한 시트 이야기</t>
         </is>
       </c>
-      <c r="F17" s="26" t="inlineStr"/>
+      <c r="F17" s="32" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1" s="6">
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>② 작동 중 사고 발생</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>작동 중 사람·반려동물·물건의 끼임·눌림·부딪힘·부상·파손이 실제로 있었는지</t>
         </is>
       </c>
-      <c r="D18" s="19" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>실제 사고 경험·목격</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr">
+      <c r="E18" s="24" t="inlineStr">
         <is>
           <t>사고 없이 가정·우려만 있음</t>
         </is>
       </c>
-      <c r="F18" s="26" t="inlineStr"/>
+      <c r="F18" s="32" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1" s="6">
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B19" s="31" t="inlineStr">
         <is>
           <t>③ 위험성·안전사고 우려</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>위험하다·조심하라·끼일 뻔했다·안전장치(센서·멈춤)가 의심된다 등 우려를 말했는지</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>우려·주의 당부·안전장치 의문</t>
         </is>
       </c>
-      <c r="E19" s="19" t="inlineStr">
+      <c r="E19" s="24" t="inlineStr">
         <is>
           <t>불편·고장만 말함</t>
         </is>
       </c>
-      <c r="F19" s="26" t="inlineStr"/>
+      <c r="F19" s="32" t="n"/>
     </row>
     <row r="20" ht="52" customHeight="1" s="6">
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>④ 타 이슈 중 일부 언급</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>여러 다른 이슈를 함께 말한 글이라도 시트 작동 위험·사고·우려가 조금이라도 포함되는지</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D20" s="24" t="inlineStr">
         <is>
           <t>한 문장이라도 있으면 해당</t>
         </is>
       </c>
-      <c r="E20" s="19" t="inlineStr">
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t>위험·사고·우려 문장이 전혀 없음</t>
         </is>
       </c>
-      <c r="F20" s="26" t="inlineStr"/>
+      <c r="F20" s="32" t="n"/>
     </row>
     <row r="21" ht="40" customHeight="1" s="6">
-      <c r="B21" s="24" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>· 최종 확정 = ① 에 해당하고, ②·③·④ 중 하나 이상에 해당하는 글.
 · 최종 확정 여부는 4항목 판정으로 정하며, 관련도는 함께 참고용으로 표시합니다.</t>
@@ -1250,173 +1264,178 @@
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" s="6">
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>3. 수집 기준</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" s="6">
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>기준</t>
         </is>
       </c>
-      <c r="D24" s="27" t="n"/>
-      <c r="E24" s="27" t="n"/>
-      <c r="F24" s="28" t="n"/>
+      <c r="D24" s="33" t="n"/>
+      <c r="E24" s="33" t="n"/>
+      <c r="F24" s="30" t="n"/>
     </row>
     <row r="25" ht="50" customHeight="1" s="6">
-      <c r="B25" s="29" t="inlineStr">
+      <c r="B25" s="34" t="inlineStr">
         <is>
           <t>수집 기간</t>
         </is>
       </c>
-      <c r="C25" s="19" t="inlineStr">
+      <c r="C25" s="24" t="inlineStr">
         <is>
           <t>{{period}}</t>
         </is>
       </c>
-      <c r="D25" s="30" t="n"/>
-      <c r="E25" s="30" t="n"/>
-      <c r="F25" s="30" t="n"/>
+      <c r="D25" s="32" t="n"/>
+      <c r="E25" s="32" t="n"/>
+      <c r="F25" s="32" t="n"/>
     </row>
     <row r="26" ht="180" customHeight="1" s="6">
-      <c r="B26" s="29" t="inlineStr">
+      <c r="B26" s="34" t="inlineStr">
         <is>
           <t>조사 채널</t>
         </is>
       </c>
-      <c r="C26" s="19" t="inlineStr">
+      <c r="C26" s="24" t="inlineStr">
         <is>
           <t>{{cafes}}</t>
         </is>
       </c>
-      <c r="D26" s="30" t="n"/>
-      <c r="E26" s="30" t="n"/>
-      <c r="F26" s="30" t="n"/>
+      <c r="D26" s="32" t="n"/>
+      <c r="E26" s="32" t="n"/>
+      <c r="F26" s="32" t="n"/>
     </row>
     <row r="28" ht="24" customHeight="1" s="6">
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>4. 포함 여부(온라인동향 / 로데이터) · 누락 사유 기준</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1" s="6">
-      <c r="B29" s="17" t="inlineStr">
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C29" s="17" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>기준</t>
         </is>
       </c>
-      <c r="D29" s="27" t="n"/>
-      <c r="E29" s="27" t="n"/>
-      <c r="F29" s="28" t="n"/>
+      <c r="D29" s="33" t="n"/>
+      <c r="E29" s="33" t="n"/>
+      <c r="F29" s="30" t="n"/>
     </row>
     <row r="30" ht="34" customHeight="1" s="6">
-      <c r="B30" s="29" t="inlineStr">
+      <c r="B30" s="34" t="inlineStr">
         <is>
           <t>표기</t>
         </is>
       </c>
-      <c r="C30" s="19" t="inlineStr">
+      <c r="C30" s="24" t="inlineStr">
         <is>
           <t>온라인동향 / 로데이터 순서로 Y(파랑) · N(빨강). 로데이터에 없는 글로는 일일동향을 쓸 수 없어 'Y / N' 조합은 나오지 않음.</t>
         </is>
       </c>
-      <c r="D30" s="30" t="n"/>
-      <c r="E30" s="30" t="n"/>
-      <c r="F30" s="30" t="n"/>
+      <c r="D30" s="32" t="n"/>
+      <c r="E30" s="32" t="n"/>
+      <c r="F30" s="32" t="n"/>
     </row>
     <row r="31" ht="64" customHeight="1" s="6">
-      <c r="B31" s="29" t="inlineStr">
+      <c r="B31" s="34" t="inlineStr">
         <is>
           <t>누락 사유 (N / N)</t>
         </is>
       </c>
-      <c r="C31" s="19" t="inlineStr">
+      <c r="C31" s="24" t="inlineStr">
         <is>
           <t>로데이터는 실제로 발생한 사고·품질 이슈만 수집해 왔고, 일어나지 않은 일(위험 우려·가능성, 주의 당부, 끼일 뻔한 아차 상황, 작동 방식 문의, 기사·공지 공유 등)은 수집하지 않았음. 로데이터에도 없는 글은 이 기준에 근거해 글 내용상 무엇이 실제로 일어나지 않은 일이었는지를 밝혀 '~로 추정' 으로 씀. 실제 사고가 있었던 글은 품질 이슈로 보지 않았을 이유(경미함·사용 부주의 등)를 씀.</t>
         </is>
       </c>
-      <c r="D31" s="30" t="n"/>
-      <c r="E31" s="30" t="n"/>
-      <c r="F31" s="30" t="n"/>
+      <c r="D31" s="32" t="n"/>
+      <c r="E31" s="32" t="n"/>
+      <c r="F31" s="32" t="n"/>
     </row>
     <row r="32" ht="34" customHeight="1" s="6">
-      <c r="B32" s="29" t="inlineStr">
+      <c r="B32" s="34" t="inlineStr">
         <is>
           <t>누락 사유 (N / Y)</t>
         </is>
       </c>
-      <c r="C32" s="19" t="inlineStr">
+      <c r="C32" s="24" t="inlineStr">
         <is>
           <t>로데이터에는 있으나 온라인 동향에 없는 글은 '로데이터에는 수집되었으나, …' 로 시작해 온라인 동향 보고에서 빠진 이유를 '~로 추정' 으로 씀.</t>
         </is>
       </c>
-      <c r="D32" s="30" t="n"/>
-      <c r="E32" s="30" t="n"/>
-      <c r="F32" s="30" t="n"/>
+      <c r="D32" s="32" t="n"/>
+      <c r="E32" s="32" t="n"/>
+      <c r="F32" s="32" t="n"/>
     </row>
     <row r="33" ht="44" customHeight="1" s="6">
-      <c r="B33" s="29" t="inlineStr">
+      <c r="B33" s="34" t="inlineStr">
         <is>
           <t>동호회 모니터링 시작일</t>
         </is>
       </c>
-      <c r="C33" s="19" t="inlineStr">
+      <c r="C33" s="24" t="inlineStr">
         <is>
           <t>{{monitorStart}}</t>
         </is>
       </c>
-      <c r="D33" s="30" t="n"/>
-      <c r="E33" s="30" t="n"/>
-      <c r="F33" s="30" t="n"/>
+      <c r="D33" s="32" t="n"/>
+      <c r="E33" s="32" t="n"/>
+      <c r="F33" s="32" t="n"/>
     </row>
     <row r="34" ht="44" customHeight="1" s="6">
-      <c r="B34" s="29" t="inlineStr">
+      <c r="B34" s="34" t="inlineStr">
         <is>
           <t>로데이터 작성 시작일</t>
         </is>
       </c>
-      <c r="C34" s="19" t="inlineStr">
+      <c r="C34" s="24" t="inlineStr">
         <is>
           <t>{{rawStart}}</t>
         </is>
       </c>
-      <c r="D34" s="30" t="n"/>
-      <c r="E34" s="30" t="n"/>
-      <c r="F34" s="30" t="n"/>
+      <c r="D34" s="32" t="n"/>
+      <c r="E34" s="32" t="n"/>
+      <c r="F34" s="32" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="22">
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="E17:F17"/>
     <mergeCell ref="B21:F21"/>
-    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="E20:F20"/>
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="B13:F13"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B15:F15"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="E18:F18"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
